--- a/output/pdf_financials_xlsx/AZM.xlsx
+++ b/output/pdf_financials_xlsx/AZM.xlsx
@@ -1378,7 +1378,7 @@
         <v>3.35484</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.296172</v>
+        <v>-0.296172</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>1.960699</v>
@@ -1429,37 +1429,37 @@
         <v>-0.582</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.354986</v>
+        <v>-1.26705</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.612024</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.994208</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.05</v>
+        <v>-4.93012</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-6.70968</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.921398</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0.454147</v>
+        <v>-0.491997</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.072853</v>
+        <v>-1.985529</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-1.636604</v>
+        <v>-2.242944</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-1.023527</v>
+        <v>-2.125045</v>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
@@ -1679,37 +1679,37 @@
         <v>-0.817589</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.456032</v>
+        <v>-0.456032</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.306012</v>
+        <v>-1.306012</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.997104</v>
+        <v>-2.997104</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.44006</v>
+        <v>-2.44006</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.35484</v>
+        <v>-3.35484</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.296172</v>
+        <v>-0.296172</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.960699</v>
+        <v>-1.960699</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.018925</v>
+        <v>-0.018925</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.956338</v>
+        <v>-0.956338</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.30317</v>
+        <v>-0.30317</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.550759</v>
+        <v>-0.550759</v>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
@@ -1877,37 +1877,37 @@
         <v>-0.817589</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.456032</v>
+        <v>-0.456032</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.306012</v>
+        <v>-1.306012</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.997104</v>
+        <v>-2.997104</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.44006</v>
+        <v>-2.44006</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.35484</v>
+        <v>-3.35484</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.296172</v>
+        <v>-0.296172</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.960699</v>
+        <v>-1.960699</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.018925</v>
+        <v>-0.018925</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.956338</v>
+        <v>-0.956338</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.30317</v>
+        <v>-0.30317</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.550759</v>
+        <v>-0.550759</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>1.61685</v>
@@ -2067,19 +2067,19 @@
         <v>-27.252967</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>22.8016</v>
+        <v>-22.8016</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>32.6503</v>
+        <v>-32.6503</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>37.4638</v>
+        <v>-37.4638</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>34.858</v>
+        <v>-34.858</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>37.276</v>
+        <v>-37.276</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>49.017475</v>
+        <v>-49.017475</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>47.8169</v>
+        <v>-47.8169</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>3.35484</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.296172</v>
+        <v>-0.296172</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.960699</v>
@@ -2288,7 +2288,7 @@
         <v>3.356296</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.297192</v>
+        <v>-0.295152</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1.961415</v>
@@ -2431,37 +2431,37 @@
         <v>-41.5836363389538</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>43.77042186486613</v>
+        <v>156.2295781351339</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.007983743363614</v>
+        <v>197.9920162566364</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>95.99955186525519</v>
+        <v>104.0004481347448</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>7.078666642051864</v>
+        <v>192.9213333579482</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>84.37085969808854</v>
+        <v>115.6291403019115</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>65.0153148792532</v>
+        <v>134.9846851207468</v>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
@@ -49549,10 +49549,10 @@
         </is>
       </c>
       <c r="P419" s="5" t="n">
-        <v>0.30317</v>
+        <v>-0.30317</v>
       </c>
       <c r="Q419" s="5" t="n">
-        <v>0.550759</v>
+        <v>-0.550759</v>
       </c>
       <c r="R419" t="inlineStr">
         <is>
@@ -50644,10 +50644,10 @@
         </is>
       </c>
       <c r="N430" s="5" t="n">
-        <v>0.018925</v>
+        <v>-0.018925</v>
       </c>
       <c r="O430" s="5" t="n">
-        <v>0.956338</v>
+        <v>-0.956338</v>
       </c>
       <c r="P430" t="inlineStr">
         <is>
@@ -51548,10 +51548,10 @@
         </is>
       </c>
       <c r="M439" s="5" t="n">
-        <v>1.960699</v>
+        <v>-1.960699</v>
       </c>
       <c r="N439" s="5" t="n">
-        <v>0.018925</v>
+        <v>-0.018925</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
@@ -52727,10 +52727,10 @@
         </is>
       </c>
       <c r="L451" s="5" t="n">
-        <v>0.296172</v>
+        <v>-0.296172</v>
       </c>
       <c r="M451" s="5" t="n">
-        <v>1.960699</v>
+        <v>-1.960699</v>
       </c>
       <c r="N451" t="inlineStr">
         <is>
@@ -53812,10 +53812,10 @@
         </is>
       </c>
       <c r="J462" s="5" t="n">
-        <v>2.44006</v>
+        <v>-2.44006</v>
       </c>
       <c r="K462" s="5" t="n">
-        <v>3.35484</v>
+        <v>-3.35484</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -54113,10 +54113,10 @@
         </is>
       </c>
       <c r="J465" s="5" t="n">
-        <v>2.40742</v>
+        <v>-2.40742</v>
       </c>
       <c r="K465" s="5" t="n">
-        <v>3.350339</v>
+        <v>-3.350339</v>
       </c>
       <c r="L465" t="inlineStr">
         <is>
@@ -54906,16 +54906,16 @@
         </is>
       </c>
       <c r="G473" s="5" t="n">
-        <v>0.456032</v>
+        <v>-0.456032</v>
       </c>
       <c r="H473" s="5" t="n">
-        <v>1.306012</v>
+        <v>-1.306012</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>2.997104</v>
+        <v>-2.997104</v>
       </c>
       <c r="J473" s="5" t="n">
-        <v>2.44006</v>
+        <v>-2.44006</v>
       </c>
       <c r="K473" t="inlineStr">
         <is>
@@ -55109,10 +55109,10 @@
         </is>
       </c>
       <c r="H475" s="5" t="n">
-        <v>0.17275</v>
+        <v>-0.17275</v>
       </c>
       <c r="I475" s="5" t="n">
-        <v>0.077698</v>
+        <v>-0.077698</v>
       </c>
       <c r="J475" t="inlineStr">
         <is>
@@ -55309,13 +55309,13 @@
         </is>
       </c>
       <c r="H477" s="5" t="n">
-        <v>1.312443</v>
+        <v>-1.312443</v>
       </c>
       <c r="I477" s="5" t="n">
-        <v>2.983665</v>
+        <v>-2.983665</v>
       </c>
       <c r="J477" s="5" t="n">
-        <v>2.407421</v>
+        <v>-2.407421</v>
       </c>
       <c r="K477" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         </is>
       </c>
       <c r="H498" s="5" t="n">
-        <v>0.17275</v>
+        <v>-0.17275</v>
       </c>
       <c r="I498" t="inlineStr">
         <is>
@@ -57708,10 +57708,10 @@
         </is>
       </c>
       <c r="G501" s="5" t="n">
-        <v>0.455577</v>
+        <v>-0.455577</v>
       </c>
       <c r="H501" s="5" t="n">
-        <v>1.312443</v>
+        <v>-1.312443</v>
       </c>
       <c r="I501" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AZM.xlsx
+++ b/output/pdf_financials_xlsx/AZM.xlsx
@@ -1093,43 +1093,43 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007577</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.013316</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.036838</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.028918</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.03208</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.031686</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014647</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017758</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016817</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.030478</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.043746</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.043826</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.054578</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -2070,42 +2070,34 @@
         <v>-22.8016</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-32.6503</v>
+        <v>36.097963</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-37.4638</v>
+        <v>36.470328</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-34.858</v>
+        <v>36.703205</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-37.276</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>37.636996</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>38.490821</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-49.017475</v>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>45.459496</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>47.548811</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-47.8169</v>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>51.762268</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>61.591639</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>70.62660200000001</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -2135,43 +2127,43 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.676838</v>
+        <v>-2.684415</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.399589</v>
+        <v>-1.412905</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.811018</v>
+        <v>0.8478560000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.306012</v>
+        <v>1.33493</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.997104</v>
+        <v>3.029184</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.49006</v>
+        <v>2.521746</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.35484</v>
+        <v>3.369487</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.296172</v>
+        <v>-0.278414</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.960699</v>
+        <v>1.977516</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.473072</v>
+        <v>0.5035500000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.029191</v>
+        <v>1.072937</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.939774</v>
+        <v>1.9836</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.574286</v>
+        <v>1.628864</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -2267,43 +2259,43 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.674023</v>
+        <v>-2.6816</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.397619</v>
+        <v>-1.410935</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.8143280000000001</v>
+        <v>0.851166</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.310259</v>
+        <v>1.339177</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.000076</v>
+        <v>3.032156</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.49214</v>
+        <v>2.523826</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.356296</v>
+        <v>3.370943</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.295152</v>
+        <v>-0.277394</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.961415</v>
+        <v>1.978232</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.473572</v>
+        <v>0.50405</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.029543</v>
+        <v>1.073289</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.940122</v>
+        <v>1.983948</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.574974</v>
+        <v>1.629552</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -48742,7 +48734,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -49696,7 +49688,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -50801,7 +50793,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -51710,7 +51702,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -52894,7 +52886,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -54290,7 +54282,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -55492,7 +55484,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -55593,7 +55585,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -59702,7 +59694,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E521" s="5" t="n">

--- a/output/pdf_financials_xlsx/AZM.xlsx
+++ b/output/pdf_financials_xlsx/AZM.xlsx
@@ -2193,43 +2193,43 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.002815</v>
+        <v>0.025714</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.00197</v>
+        <v>0.018847</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.00331</v>
+        <v>0.01759</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.004247</v>
+        <v>0.016437</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.002972</v>
+        <v>0.011804</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.00208</v>
+        <v>0.008503999999999999</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.001456</v>
+        <v>0.006144</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.00102</v>
+        <v>0.004456</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.0007159999999999999</v>
+        <v>0.003917</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.004352</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.000352</v>
+        <v>0.008753</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.000348</v>
+        <v>0.060312</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.000688</v>
+        <v>0.06036</v>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
@@ -2259,43 +2259,43 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.6816</v>
+        <v>-2.658701</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.410935</v>
+        <v>-1.394058</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.851166</v>
+        <v>0.865446</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.339177</v>
+        <v>1.351367</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.032156</v>
+        <v>3.040988</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.523826</v>
+        <v>2.53025</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.370943</v>
+        <v>3.375631</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.277394</v>
+        <v>-0.273958</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.978232</v>
+        <v>1.981433</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.50405</v>
+        <v>0.507902</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.073289</v>
+        <v>1.08169</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.983948</v>
+        <v>2.043912</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.629552</v>
+        <v>1.689224</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -6425,55 +6425,55 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.025714</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.018847</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.01759</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.016437</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.011804</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.008503999999999999</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.006144</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.004456</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.003917</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.004352</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.008753</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.060312</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.06036</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.061988</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.07951</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.100868</v>
       </c>
     </row>
     <row r="101">
@@ -29987,7 +29987,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -30086,7 +30090,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
@@ -30157,7 +30161,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -32138,7 +32146,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -34518,7 +34530,11 @@
           <t>Depreciation of property and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -34617,7 +34633,11 @@
           <t>Depreciation of right-of-use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -35730,7 +35750,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -36650,7 +36674,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E289" s="5" t="n">
         <v>0.022899</v>
       </c>
@@ -38267,7 +38295,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -58789,7 +58821,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E512" s="5" t="n">
         <v>0.022899</v>
       </c>
@@ -58890,7 +58926,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E513" s="5" t="n">

--- a/output/pdf_financials_xlsx/AZM.xlsx
+++ b/output/pdf_financials_xlsx/AZM.xlsx
@@ -1450,16 +1450,16 @@
         <v>-3.921398</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0.491997</v>
+        <v>0.454147</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-1.985529</v>
+        <v>0.072853</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-2.242944</v>
+        <v>1.636604</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-2.125045</v>
+        <v>1.023527</v>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
@@ -2444,16 +2444,16 @@
         <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>104.0004481347448</v>
+        <v>95.99955186525519</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>192.9213333579482</v>
+        <v>7.078666642051864</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>115.6291403019115</v>
+        <v>84.37085969808854</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>134.9846851207468</v>
+        <v>65.0153148792532</v>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
@@ -3897,52 +3897,52 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.40291</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.41503</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.753</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>0.791896</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>0.785988</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>0.732143</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>0.63274</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>0.72012</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>0.706097</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>0.73123</v>
       </c>
       <c r="M56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>1.485366</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>2.47035</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>2.728075</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>3.055986</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0</v>
+        <v>3.065688</v>
       </c>
     </row>
     <row r="57">
@@ -3955,52 +3955,52 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.120488</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.322475</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.441083</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.521695</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.600287</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.581852</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.599008</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.6119289999999999</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>0.609453</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>0.653829</v>
       </c>
       <c r="M57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>0.849376</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>0.920288</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>1.190204</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>1.548912</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>0</v>
+        <v>1.914058</v>
       </c>
     </row>
     <row r="58">
@@ -4741,22 +4741,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.246064</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.04522</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.036976</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.054485</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.050673</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.066386</v>
       </c>
     </row>
     <row r="71">
@@ -4799,22 +4799,22 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.246064</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.04522</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.036976</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.054485</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.050673</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.066386</v>
       </c>
     </row>
     <row r="72">
@@ -5031,22 +5031,22 @@
         <v>0.8724690000000001</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>1.906925</v>
+        <v>1.660861</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>3.736637</v>
+        <v>3.691417</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.495172</v>
+        <v>0.458196</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.272094</v>
+        <v>0.217609</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1.180098</v>
+        <v>1.129425</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>3.111315</v>
+        <v>3.044929</v>
       </c>
     </row>
     <row r="76">
@@ -5345,24 +5345,22 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.008166032147153472</v>
+        <v>0.02510013296005418</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.001656529620296108</v>
+        <v>0.002676550174093734</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.0007729056936135439</v>
+        <v>0.00155670693674487</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.001163973290084026</v>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002415534008236618</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.001018310538956422</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.004493948430472482</v>
+        <v>0.005668769591708147</v>
       </c>
     </row>
     <row r="81">
@@ -7301,13 +7299,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.086006</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.024317</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -7316,34 +7314,34 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.114592</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.08744300000000001</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.049648</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.012828</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.00055</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.069285</v>
       </c>
     </row>
     <row r="116">
@@ -10181,7 +10179,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -15913,7 +15915,11 @@
           <t>Lease liabilities (Note 12)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18616,7 +18622,11 @@
           <t>Lease liabilities (Note 11)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -21103,7 +21113,11 @@
           <t>Lease liabilities (Note 9)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -32649,7 +32663,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -36035,7 +36053,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -37303,7 +37325,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -37402,7 +37428,11 @@
           <t>Flow-through private placement</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -38501,7 +38531,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -40202,7 +40236,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -46568,7 +46606,11 @@
           <t>Recovery of future income taxes</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -49413,7 +49455,11 @@
           <t>Deferred income tax recovery (Notes 11c and 16)</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -50518,7 +50564,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -51425,7 +51475,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
